--- a/team_task_tracker.xlsx
+++ b/team_task_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/busyraoryza/Proton/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34D8E66-C8A7-0F4F-AB14-6EE5CB37243A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ADDFB6-F99B-5F4C-B782-1988FF0679AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26080" windowHeight="15100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="171">
   <si>
     <t>TEAM TASK &amp; PRODUCTIVITY TRACKER</t>
   </si>
@@ -539,6 +539,21 @@
   </si>
   <si>
     <t>Pet</t>
+  </si>
+  <si>
+    <t>TSK-037</t>
+  </si>
+  <si>
+    <t>TSK-038</t>
+  </si>
+  <si>
+    <t>TSK-039</t>
+  </si>
+  <si>
+    <t>TSK-040</t>
+  </si>
+  <si>
+    <t>TSK-041</t>
   </si>
 </sst>
 </file>
@@ -548,7 +563,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +646,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -711,11 +732,6 @@
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,6 +809,11 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1057,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1070,1205 +1091,1350 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <v>46117</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <v>46123</v>
       </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="6"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="13">
         <v>46115</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="13">
         <v>46124</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <v>46133</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="7">
         <v>46153</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="13">
         <v>46113</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="13">
         <v>46121</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="13">
         <v>46118</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <v>46116</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="7">
         <v>46121</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="7">
         <v>46118</v>
       </c>
-      <c r="K9" s="6"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="13">
         <v>46136</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="13">
         <v>46153</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="13">
         <v>46153</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>46124</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="7">
         <v>46145</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="6"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="13">
         <v>46115</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="13">
         <v>46125</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="13">
         <v>46125</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>46124</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="7">
         <v>46138</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="6"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="13">
         <v>46132</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="13">
         <v>46140</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="12"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="7">
         <v>46133</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="7">
         <v>46153</v>
       </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="6"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="13">
         <v>46123</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="13">
         <v>46138</v>
       </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="12"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="7">
         <v>46135</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="7">
         <v>46148</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="6"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="13">
         <v>46117</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="13">
         <v>46128</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="12"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="7">
         <v>46131</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="7">
         <v>46147</v>
       </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="6"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="13">
         <v>46129</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="13">
         <v>46147</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="12"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="7">
         <v>46134</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="7">
         <v>46150</v>
       </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="6"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="13">
         <v>46129</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="13">
         <v>46140</v>
       </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="12"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="7">
         <v>46130</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="7">
         <v>46141</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="7">
         <v>46139</v>
       </c>
-      <c r="K23" s="6"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="13">
         <v>46136</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="13">
         <v>46147</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="12"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="7">
         <v>46122</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="7">
         <v>46141</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="7">
         <v>46140</v>
       </c>
-      <c r="K25" s="6"/>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="13">
         <v>46129</v>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="13">
         <v>46132</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="13">
         <v>46130</v>
       </c>
-      <c r="K26" s="12"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="7">
         <v>46138</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="7">
         <v>46150</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="7">
         <v>46149</v>
       </c>
-      <c r="K27" s="6"/>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="13">
         <v>46128</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="13">
         <v>46133</v>
       </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="12"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="7">
         <v>46118</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="7">
         <v>46129</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="6"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="13">
         <v>46137</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="13">
         <v>46146</v>
       </c>
-      <c r="J30" s="13"/>
-      <c r="K30" s="12"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="7">
         <v>46127</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="7">
         <v>46146</v>
       </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="6"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="13">
         <v>46131</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="13">
         <v>46151</v>
       </c>
-      <c r="J32" s="13"/>
-      <c r="K32" s="12"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="7">
         <v>46114</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="7">
         <v>46124</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="7">
         <v>46124</v>
       </c>
-      <c r="K33" s="6"/>
+      <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="13">
         <v>46128</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="13">
         <v>46137</v>
       </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="12"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="7">
         <v>46128</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="7">
         <v>46138</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="6"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H36" s="16">
+      <c r="H36" s="13">
         <v>46124</v>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="13">
         <v>46140</v>
       </c>
-      <c r="J36" s="13"/>
-      <c r="K36" s="12"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="7">
         <v>46133</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="7">
         <v>46139</v>
       </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="6"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="13">
         <v>46120</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="13">
         <v>46129</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="13">
         <v>46128</v>
       </c>
-      <c r="K38" s="12"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="7">
         <v>46120</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="7">
         <v>46125</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="6"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="23" t="s">
+      <c r="G40" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H40" s="16">
+      <c r="H40" s="13">
         <v>46113</v>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="13">
         <v>46118</v>
       </c>
-      <c r="J40" s="13"/>
-      <c r="K40" s="12"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I41" s="13">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I42" s="13">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I43" s="13">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I44" s="13">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45" s="13">
+        <v>46113</v>
+      </c>
+      <c r="I45" s="13">
+        <v>46118</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:K40" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2276,6 +2442,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" errorTitle="Invalid Status" error="Please select a valid status" sqref="G5:G200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not Started,In Progress,In Review,Completed,On Hold"</formula1>
@@ -2303,192 +2470,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="21" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="22">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="22">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="22">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="22">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="23">
         <v>7</v>
       </c>
     </row>
@@ -2511,75 +2678,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="21" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="15" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2602,522 +2769,522 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="25">
         <f>COUNTA('Task Tracker'!A5:A200)</f>
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="25">
         <f>COUNTIF('Task Tracker'!G5:G200,"Completed")</f>
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="25">
         <f>COUNTIF('Task Tracker'!G5:G200,"In Progress")</f>
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="25">
         <f ca="1">COUNTIFS('Task Tracker'!I5:I200,"&lt;"&amp;TODAY(),'Task Tracker'!G5:G200,"&lt;&gt;Completed")</f>
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="26" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="21" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A10)</f>
         <v>3</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A10,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>1</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A10,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A10,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A10,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A11)</f>
         <v>3</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A11,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>2</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A11,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A11,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A11,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A12)</f>
         <v>2</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A12,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A12,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A12,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A12,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A13)</f>
         <v>6</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A13,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>1</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A13,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A13,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>2</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A13,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A14)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A14,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A14,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A14,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>1</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A14,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A15)</f>
         <v>1</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A15,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A15,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A15,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A15,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A16)</f>
         <v>4</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A16,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A16,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A16,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>2</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A16,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A17)</f>
-        <v>4</v>
-      </c>
-      <c r="C17" s="25">
+        <v>9</v>
+      </c>
+      <c r="C17" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A17,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A17,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A17,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>1</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A17,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A18)</f>
         <v>7</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A18,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A18,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>2</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A18,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>1</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A18,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A19)</f>
         <v>2</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A19,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A19,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A19,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A19,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A20)</f>
         <v>2</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A20,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>1</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A20,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>1</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A20,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A20,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="22">
         <f>COUNTIF('Task Tracker'!C$5:C$200,A21)</f>
         <v>1</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A21,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A21,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A21,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>1</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="22">
         <f>COUNTIFS('Task Tracker'!C$5:C$200,A21,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="26" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24" t="s">
+      <c r="A25" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="21" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="22">
         <f>COUNTIF('Task Tracker'!D$5:D$200,A26)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A26,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A26,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A26,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A26,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="22">
         <f>COUNTIF('Task Tracker'!D$5:D$200,A27)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A27,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A27,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A27,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A27,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="22">
         <f>COUNTIF('Task Tracker'!D$5:D$200,A28)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A28,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A28,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A28,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A28,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="22">
         <f>COUNTIF('Task Tracker'!D$5:D$200,A29)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A29,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A29,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A29,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A29,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="22">
         <f>COUNTIF('Task Tracker'!D$5:D$200,A30)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A30,'Task Tracker'!G$5:G$200,"Not Started")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A30,'Task Tracker'!G$5:G$200,"In Progress")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A30,'Task Tracker'!G$5:G$200,"In Review")</f>
         <v>0</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="22">
         <f>COUNTIFS('Task Tracker'!D$5:D$200,A30,'Task Tracker'!G$5:G$200,"Completed")</f>
         <v>0</v>
       </c>
